--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/ene-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/ene-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>78828</v>
+        <v>76983.95</v>
       </c>
     </row>
     <row r="3">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>387809.16</v>
+        <v>382886.76</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>46111.52</v>
+        <v>45526.23</v>
       </c>
     </row>
     <row r="5">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>29308.25</v>
+        <v>28936.25</v>
       </c>
     </row>
     <row r="6">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>23816.27</v>
+        <v>23769.37</v>
       </c>
     </row>
     <row r="7">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>38194.57</v>
+        <v>38194.82</v>
       </c>
     </row>
     <row r="8">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>38780.92</v>
+        <v>38781.17</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>71218.82000000001</v>
+        <v>70974.39999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>21662.27</v>
+        <v>21587.92</v>
       </c>
     </row>
     <row r="11">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>124884.17</v>
+        <v>124455.56</v>
       </c>
     </row>
     <row r="12">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>35319.24</v>
+        <v>35097.92</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>36638.34</v>
+        <v>37529.31</v>
       </c>
     </row>
     <row r="14">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>21432.95</v>
+        <v>21954.15</v>
       </c>
     </row>
     <row r="15">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>46936.21</v>
+        <v>48077.59</v>
       </c>
     </row>
     <row r="16">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>27049.47</v>
+        <v>27869.69</v>
       </c>
     </row>
     <row r="17">
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>40858.43</v>
+        <v>42097.39</v>
       </c>
     </row>
     <row r="18">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>26461.43</v>
+        <v>27247.95</v>
       </c>
     </row>
     <row r="19">
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>57937.89</v>
+        <v>59659.98</v>
       </c>
     </row>
     <row r="20">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>36638.34</v>
+        <v>37727.35</v>
       </c>
     </row>
     <row r="21">
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>34154.59</v>
+        <v>35169.77</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/ene-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/ene-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -625,7 +625,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/ene-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/ene-2026.xlsx
@@ -792,7 +792,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NIQUEN</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/ene-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/ene-2026.xlsx
@@ -562,7 +562,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -688,7 +692,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -749,7 +757,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -810,7 +822,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -871,7 +887,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -932,7 +952,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -993,7 +1017,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1054,7 +1082,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1180,7 +1212,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1241,7 +1277,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1302,7 +1342,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1363,7 +1407,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1424,7 +1472,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1485,7 +1537,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1546,7 +1602,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1607,7 +1667,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1668,7 +1732,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/ene-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/ene-2026.xlsx
@@ -1119,7 +1119,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
